--- a/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-234400</t>
+          <t>I-234400</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-234403</t>
+          <t>I-471771</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,17 +560,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-17.9765028</t>
+          <t>-17.9835835</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-70.2376331</t>
+          <t>-70.2406018</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Expedición Libertadora / Pasaje Sabancaya</t>
+          <t>Avenida Emancipación / Calle Baquíjano y Carrillo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-234415</t>
+          <t>I-472330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-17.9762818</t>
+          <t>-17.9741587</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-70.2373112</t>
+          <t>-70.2334553</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Expedición Libertadora / Avenida los Proceres</t>
+          <t>Calle La Unión / Pasaje Huatasani</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-402385</t>
+          <t>I-472373</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-17.9820864</t>
+          <t>-17.9780494</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-70.2258426</t>
+          <t>-70.2374623</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Artesanal A / Avenida Artesanal B</t>
+          <t>Avenida Maria Parado de Bellido / Calle Gabriel Aguilar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-471641</t>
+          <t>I-472574</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,17 +716,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-17.9799974</t>
+          <t>-17.9793735</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-70.2346129</t>
+          <t>-70.2344263</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida los Proceres / Calle Juan Jose Crespo y Castillo</t>
+          <t>Avenida Emancipación / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-471771</t>
+          <t>I-472592</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-17.9835835</t>
+          <t>-17.979361</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-70.2406018</t>
+          <t>-70.2350753</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Emancipación / Calle Baquíjano y Carrillo</t>
+          <t>Avenida los Proceres / Calle Mateo Silva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-472238</t>
+          <t>I-731430</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-17.9735893</t>
+          <t>-17.9856607</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-70.2338811</t>
+          <t>-70.2333699</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Calle Chucuito / Pasaje Kelluyo</t>
+          <t>Avenida Aviación / Calle Daniel Alcides Carrion</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-472239</t>
+          <t>I-85288</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -872,22 +872,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-17.9738984</t>
+          <t>-17.9837268</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-70.2336699</t>
+          <t>-70.2302922</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Expedición Libertadora / Pasaje Kelluyo</t>
+          <t>Avenida El Sol / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>l-472241</t>
+          <t>I-85292</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -924,22 +924,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-17.9736663</t>
+          <t>-17.9870105</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-70.2333239</t>
+          <t>-70.2345962</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Expedición Libertadora / Pasaje Zepita</t>
+          <t>Avenida El Sol / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -951,7 +951,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>l-472328</t>
+          <t>I-472637</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -976,22 +976,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-17.9739954</t>
+          <t>-17.9787119</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-70.233222</t>
+          <t>-70.2334752</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle La Unión / Pasaje Taraco</t>
+          <t>Avenida Emancipación / Calle Hermanos Angulo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>l-472330</t>
+          <t>I-472635</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-17.9741587</t>
+          <t>-17.9807952</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-70.2334553</t>
+          <t>-70.2319712</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Calle La Unión / Pasaje Huatasani</t>
+          <t>Calle Hermanos Angulo / Calle Manuel Lorenzo de Vidaurre</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l-472371</t>
+          <t>I-472630</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1080,22 +1080,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-17.9784501</t>
+          <t>-17.9799045</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-70.2371953</t>
+          <t>-70.2312982</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida Maria Parado de Bellido / Avenida Mariano Necochea</t>
+          <t>Avenida Los Precursores / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1107,7 +1107,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>l-472372</t>
+          <t>I-472626</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1132,22 +1132,22 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-17.9783549</t>
+          <t>-17.9787454</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-70.2372377</t>
+          <t>-70.2321323</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Maria Parado de Bellido / Avenida Mariano Necochea</t>
+          <t>Avenida Los Precursores / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>l-472373</t>
+          <t>I-472617</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-17.9780494</t>
+          <t>-17.9830521</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-70.2374623</t>
+          <t>-70.2391019</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Avenida Maria Parado de Bellido / Calle Gabriel Aguilar</t>
+          <t>Calle Juan Jose Crespo y Castillo / Pasaje Virgen de Chapi</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>l-472498</t>
+          <t>I-472658</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1236,22 +1236,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-17.9812668</t>
+          <t>-17.9828119</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-70.2346311</t>
+          <t>-70.2349484</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Avenida Internacional / Calle Rosa Merino</t>
+          <t>Calle Manuel Lorenzo de Vidaurre / Pasaje Francisco Garcia Calderon</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>l-472501</t>
+          <t>I-472666</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-17.9817031</t>
+          <t>-17.9819274</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-70.2352832</t>
+          <t>-70.2312331</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Avenida Internacional / Pasaje Juan Manuel Iturregui</t>
+          <t>Calle Hermanos Angulo / Calle s / n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1307,630 +1307,6 @@
         </is>
       </c>
       <c r="J17" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>l-472574</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-17.9793735</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-70.2344263</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Avenida Emancipación</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>l-472592</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-17.979361</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-70.2350753</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Avenida los Proceres / Calle Mateo Silva</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>l-472621</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-17.9836953</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-70.2400636</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Calle Juan Jose Crespo y Castillo / Pasaje Augusto Bolognesi</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>l-472653</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-17.9813434</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-70.2345801</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Avenida Internacional / Calle Rosa Merino</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>l-472657</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-17.9817809</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-70.2352275</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Avenida Internacional / Pasaje Juan Manuel Iturregui</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>l-472723</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-17.9796592</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-70.2348581</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Avenida Emancipación / Avenida los Proceres</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>l-731430</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-17.9856607</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-70.2333699</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Avenida Aviación / Calle Daniel Alcides Carrion</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>l-731699</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-17.9815667</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-70.2349105</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Avenida Internacional / Avenida Maria Parado de Bellido</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>l-745672</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-17.9817506</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-70.2257641</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Avenida Artesanal A</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>l-812989</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-17.981489</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-70.2349631</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Avenida Internacional / Avenida Maria Parado de Bellido</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>l-85290</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-17.9860021</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-70.233131</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Avenida El Sol / Calle Daniel Alcides Carrion / Calle Daniel Alcides Carrión</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>l-87288</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-17.9860867</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-70.2330731</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Avenida El Sol / Calle Daniel Alcides Carrión</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
         <is>
           <t>230104</t>
         </is>

--- a/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,6 +1312,266 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-85297</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CIUDAD NUEVA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-17.9846673</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-70.2311935</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Avenida El Sol / Avenida los Proceres</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-472602</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CIUDAD NUEVA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-17.9801341</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-70.2374182</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle Daniel Alcides Carrion / Calle Toribio Luzuriaga</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-472598</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CIUDAD NUEVA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-17.9798135</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-70.2376469</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle Daniel Alcides Carrion / Calle Manuel de Avalos</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-472597</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CIUDAD NUEVA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-17.9804653</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-70.2385773</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle Hipolito Unanue / Calle Manuel de Avalos</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-472596</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CIUDAD NUEVA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-17.9784708</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-70.2357295</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Avenida los Proceres / Calle Manuel de Avalos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,7 +882,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida El Sol / Calle s / n</t>
+          <t>Avenida Aviación / Avenida El Sol / Calle Juan Santos Atahualpa</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1567,6 +1567,214 @@
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-85298</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>CIUDAD NUEVA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-17.9853445</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-70.2321673</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Avenida El Sol / Avenida Maria Parado de Bellido</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-472672</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CIUDAD NUEVA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-17.9837066</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-70.2338655</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle Miguel Iglesias / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I-472607</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CIUDAD NUEVA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-17.9821726</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-70.2368585</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Pasaje Pablo de Olavide / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I-472606</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CIUDAD NUEVA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-17.9819572</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-70.2365485</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Pasaje Juan Espinoza Medrano / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>230104</t>
         </is>

--- a/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-234400</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-17.9760353</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-471771</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-17.9835835</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-472330</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-17.9741587</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-472373</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-17.9780494</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-472574</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-17.9793735</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-472592</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-17.979361</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-731430</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-17.9856607</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-85288</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-17.9837268</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-85292</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-17.9870105</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-472637</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-17.9787119</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-472635</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-17.9807952</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-472630</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-17.9799045</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-472626</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-17.9787454</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-472617</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-17.9830521</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-472658</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-17.9828119</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-472666</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-17.9819274</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-85297</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-17.9846673</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-472602</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-17.9801341</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-472598</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-17.9798135</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-472597</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-17.9804653</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-472596</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-17.9784708</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-85298</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-17.9853445</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-472672</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-17.9837066</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-472607</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-17.9821726</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>230104</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CIUDAD_NUEVA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-472606</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>230104</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>CIUDAD NUEVA</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-17.9819572</t>
@@ -1772,11 +1647,6 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>230104</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CIUDAD_NUEVA</t>
+          <t>CIUDAD NUEVA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">

--- a/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
+++ b/Intersecciones/excels/TACNA-TACNA-CIUDAD_NUEVA.xlsx
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-234400</t>
+          <t>I-85298</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-17.9760353</t>
+          <t>-17.9853445</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-70.2369521</t>
+          <t>-70.2321673</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Expedición Libertadora / Calle Las Buganvillas</t>
+          <t>Avenida El Sol / Avenida Maria Parado de Bellido</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-471771</t>
+          <t>I-85297</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-17.9835835</t>
+          <t>-17.9846673</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-70.2406018</t>
+          <t>-70.2311935</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Emancipación / Calle Baquíjano y Carrillo</t>
+          <t>Avenida El Sol / Avenida los Proceres</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-472330</t>
+          <t>I-85292</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-17.9741587</t>
+          <t>-17.9870105</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-70.2334553</t>
+          <t>-70.2345962</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Calle La Unión / Pasaje Huatasani</t>
+          <t>Avenida El Sol / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -627,27 +627,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-472373</t>
+          <t>I-85288</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-17.9780494</t>
+          <t>-17.9837268</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-70.2374623</t>
+          <t>-70.2302922</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Maria Parado de Bellido / Calle Gabriel Aguilar</t>
+          <t>Avenida El Sol / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-472574</t>
+          <t>I-731430</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-17.9793735</t>
+          <t>-17.9856607</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-70.2344263</t>
+          <t>-70.2333699</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Emancipación / Calle s / n</t>
+          <t>Avenida Aviación / Calle Daniel Alcides Carrion</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,27 +721,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-472592</t>
+          <t>I-472672</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-17.979361</t>
+          <t>-17.9837066</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-70.2350753</t>
+          <t>-70.2338655</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida los Proceres / Calle Mateo Silva</t>
+          <t>Calle Miguel Iglesias / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -768,27 +768,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-731430</t>
+          <t>I-472666</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-17.9856607</t>
+          <t>-17.9819274</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-70.2333699</t>
+          <t>-70.2312331</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Aviación / Calle Daniel Alcides Carrion</t>
+          <t>Calle Hermanos Angulo / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-85288</t>
+          <t>I-472658</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-17.9837268</t>
+          <t>-17.9828119</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-70.2302922</t>
+          <t>-70.2349484</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Aviación / Avenida El Sol / Calle Juan Santos Atahualpa</t>
+          <t>Calle Manuel Lorenzo de Vidaurre / Pasaje Francisco Garcia Calderon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,22 +862,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-85292</t>
+          <t>I-472637</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-17.9870105</t>
+          <t>-17.9787119</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-70.2345962</t>
+          <t>-70.2334752</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida El Sol / Calle s / n</t>
+          <t>Avenida Emancipación / Calle Hermanos Angulo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -909,22 +909,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-472637</t>
+          <t>I-472635</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-17.9787119</t>
+          <t>-17.9807952</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-70.2334752</t>
+          <t>-70.2319712</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Emancipación / Calle Hermanos Angulo</t>
+          <t>Calle Hermanos Angulo / Calle Manuel Lorenzo de Vidaurre</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-472635</t>
+          <t>I-472630</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-17.9807952</t>
+          <t>-17.9799045</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-70.2319712</t>
+          <t>-70.2312982</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Calle Hermanos Angulo / Calle Manuel Lorenzo de Vidaurre</t>
+          <t>Avenida Los Precursores / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-472630</t>
+          <t>I-472626</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-17.9799045</t>
+          <t>-17.9787454</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-70.2312982</t>
+          <t>-70.2321323</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-472626</t>
+          <t>I-472617</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-17.9787454</t>
+          <t>-17.9830521</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-70.2321323</t>
+          <t>-70.2391019</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Los Precursores / Calle s / n</t>
+          <t>Calle Juan Jose Crespo y Castillo / Pasaje Virgen de Chapi</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1097,22 +1097,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-472617</t>
+          <t>I-472607</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-17.9830521</t>
+          <t>-17.9821726</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-70.2391019</t>
+          <t>-70.2368585</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Calle Juan Jose Crespo y Castillo / Pasaje Virgen de Chapi</t>
+          <t>Pasaje Pablo de Olavide / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-472658</t>
+          <t>I-472606</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-17.9828119</t>
+          <t>-17.9819572</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-70.2349484</t>
+          <t>-70.2365485</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Calle Manuel Lorenzo de Vidaurre / Pasaje Francisco Garcia Calderon</t>
+          <t>Pasaje Juan Espinoza Medrano / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-472666</t>
+          <t>I-472602</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-17.9819274</t>
+          <t>-17.9801341</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-70.2312331</t>
+          <t>-70.2374182</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Calle Hermanos Angulo / Calle s / n</t>
+          <t>Calle Daniel Alcides Carrion / Calle Toribio Luzuriaga</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-85297</t>
+          <t>I-472598</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-17.9846673</t>
+          <t>-17.9798135</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-70.2311935</t>
+          <t>-70.2376469</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida El Sol / Avenida los Proceres</t>
+          <t>Calle Daniel Alcides Carrion / Calle Manuel de Avalos</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-472602</t>
+          <t>I-472597</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-17.9801341</t>
+          <t>-17.9804653</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-70.2374182</t>
+          <t>-70.2385773</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Calle Daniel Alcides Carrion / Calle Toribio Luzuriaga</t>
+          <t>Calle Hipolito Unanue / Calle Manuel de Avalos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1332,22 +1332,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-472598</t>
+          <t>I-472596</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-17.9798135</t>
+          <t>-17.9784708</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-70.2376469</t>
+          <t>-70.2357295</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Calle Daniel Alcides Carrion / Calle Manuel de Avalos</t>
+          <t>Avenida los Proceres / Calle Manuel de Avalos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1379,27 +1379,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-472597</t>
+          <t>I-472592</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-17.9804653</t>
+          <t>-17.979361</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-70.2385773</t>
+          <t>-70.2350753</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Calle Hipolito Unanue / Calle Manuel de Avalos</t>
+          <t>Avenida los Proceres / Calle Mateo Silva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1426,27 +1426,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-472596</t>
+          <t>I-472574</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-17.9784708</t>
+          <t>-17.9793735</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-70.2357295</t>
+          <t>-70.2344263</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Avenida los Proceres / Calle Manuel de Avalos</t>
+          <t>Avenida Emancipación / Calle s / n</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1473,27 +1473,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-85298</t>
+          <t>I-472373</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-17.9853445</t>
+          <t>-17.9780494</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-70.2321673</t>
+          <t>-70.2374623</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Avenida El Sol / Avenida Maria Parado de Bellido</t>
+          <t>Avenida Maria Parado de Bellido / Calle Gabriel Aguilar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1520,27 +1520,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-472672</t>
+          <t>I-472330</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-17.9837066</t>
+          <t>-17.9741587</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-70.2338655</t>
+          <t>-70.2334553</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Calle Miguel Iglesias / Calle s / n</t>
+          <t>Calle La Unión / Pasaje Huatasani</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-472607</t>
+          <t>I-471771</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-17.9821726</t>
+          <t>-17.9835835</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-70.2368585</t>
+          <t>-70.2406018</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pasaje Pablo de Olavide / Calle s / n</t>
+          <t>Avenida Emancipación / Calle Baquíjano y Carrillo</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1614,27 +1614,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-472606</t>
+          <t>I-234400</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-17.9819572</t>
+          <t>-17.9760353</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-70.2365485</t>
+          <t>-70.2369521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pasaje Juan Espinoza Medrano / Calle s / n</t>
+          <t>Avenida Expedición Libertadora / Calle Las Buganvillas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
